--- a/data/trans_dic/P64D$particular_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,56; 71,96</t>
+          <t>60,46; 71,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,13; 72,37</t>
+          <t>63,0; 72,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,59; 70,61</t>
+          <t>63,44; 70,7</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,48; 76,19</t>
+          <t>64,58; 76,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>58,07; 69,07</t>
+          <t>57,93; 69,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,83; 71,59</t>
+          <t>63,84; 71,72</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75,44; 96,81</t>
+          <t>74,65; 97,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,86; 58,98</t>
+          <t>39,37; 60,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,09; 95,15</t>
+          <t>68,69; 93,39</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,9; 82,01</t>
+          <t>73,74; 81,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>56,09; 64,4</t>
+          <t>55,34; 64,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66,83; 72,96</t>
+          <t>67,19; 73,23</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>77,1; 87,26</t>
+          <t>75,91; 87,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,68; 68,04</t>
+          <t>29,3; 68,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>42,85; 74,5</t>
+          <t>43,92; 74,51</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,04; 85,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,64; 64,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>66,08; 76,54</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>77,92%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>60,15%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>70,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>74,09; 85,72</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49,92; 64,4</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>66,08; 76,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>212457; 252430</t>
+          <t>212079; 251081</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>197346; 226218</t>
+          <t>196929; 226929</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>421833; 468446</t>
+          <t>420844; 469031</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195604; 231117</t>
+          <t>195897; 230790</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146409; 174137</t>
+          <t>146066; 174870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>354576; 397676</t>
+          <t>354623; 398406</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>369292; 473908</t>
+          <t>365429; 476121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>29180; 43181</t>
+          <t>28824; 44213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>388769; 535455</t>
+          <t>386524; 525562</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>413633; 459026</t>
+          <t>412760; 457307</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>239210; 274656</t>
+          <t>235996; 275312</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>659042; 719459</t>
+          <t>662612; 722195</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>184974; 209347</t>
+          <t>182126; 209731</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103367; 254106</t>
+          <t>109423; 255024</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>262835; 456976</t>
+          <t>269364; 456985</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2444</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1514286</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>864805</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2379091</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1438787; 1659572</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>728062; 924484</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2234122; 2587930</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>1230</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>1514286</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>864805</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>2379091</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>1439863; 1665780</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>717699; 925923</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2234171; 2591024</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P64D$particular_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,13%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>60,46; 71,57</t>
+          <t>59,96; 70,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,0; 72,6</t>
+          <t>62,55; 71,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,44; 70,7</t>
+          <t>62,08; 69,61</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,58; 76,08</t>
+          <t>65,8; 76,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>57,93; 69,36</t>
+          <t>57,57; 68,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,84; 71,72</t>
+          <t>64,03; 71,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>69,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>74,65; 97,26</t>
+          <t>69,2; 80,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>39,37; 60,39</t>
+          <t>39,44; 58,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68,69; 93,39</t>
+          <t>64,06; 74,14</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>73,74; 81,7</t>
+          <t>70,55; 78,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,34; 64,56</t>
+          <t>54,05; 62,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,19; 73,23</t>
+          <t>64,6; 70,4</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>69,18%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,91; 87,42</t>
+          <t>72,34; 83,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29,3; 68,29</t>
+          <t>55,17; 64,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,92; 74,51</t>
+          <t>65,27; 73,45</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>74,04; 85,4</t>
+          <t>70,61; 75,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,64; 64,3</t>
+          <t>58,73; 63,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>66,08; 76,54</t>
+          <t>65,98; 69,31</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>232274</t>
+          <t>248780</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>212772</t>
+          <t>223864</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445046</t>
+          <t>472644</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>212079; 251081</t>
+          <t>228833; 269547</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196929; 226929</t>
+          <t>208342; 238836</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>420844; 469031</t>
+          <t>443732; 497566</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>215695</t>
+          <t>229895</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>160403</t>
+          <t>172367</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376098</t>
+          <t>402262</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>195897; 230790</t>
+          <t>211093; 246597</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146066; 174870</t>
+          <t>157444; 186570</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>354623; 398406</t>
+          <t>380529; 427190</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>432279</t>
+          <t>204168</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>40910</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468588</t>
+          <t>245078</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>365429; 476121</t>
+          <t>187807; 219193</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28824; 44213</t>
+          <t>32725; 48195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>386524; 525562</t>
+          <t>227028; 262729</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>435929</t>
+          <t>463591</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>256929</t>
+          <t>277583</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>692858</t>
+          <t>741174</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>412760; 457307</t>
+          <t>437952; 487278</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>235996; 275312</t>
+          <t>258695; 299047</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>662612; 722195</t>
+          <t>710164; 773939</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>198109</t>
+          <t>240704</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>198393</t>
+          <t>188139</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>396501</t>
+          <t>428844</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>182126; 209731</t>
+          <t>221989; 256416</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>109423; 255024</t>
+          <t>172671; 203142</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>269364; 456985</t>
+          <t>404589; 455288</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1514286</t>
+          <t>1387139</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>864805</t>
+          <t>902864</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2379091</t>
+          <t>2290002</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1438787; 1659572</t>
+          <t>1342682; 1428342</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>728062; 924484</t>
+          <t>869836; 937494</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2234122; 2587930</t>
+          <t>2231723; 2344420</t>
         </is>
       </c>
     </row>
